--- a/ig/DM-OCTOBRE-2026/ASS-X16-CorrespondanceType-Classe-DMP.xlsx
+++ b/ig/DM-OCTOBRE-2026/ASS-X16-CorrespondanceType-Classe-DMP.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="161">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240927120000</t>
+    <t>20261102120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-27T12:00:00+01:00</t>
+    <t>2026-11-02T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -380,6 +380,12 @@
     <t>101881-1</t>
   </si>
   <si>
+    <t>85895-1</t>
+  </si>
+  <si>
+    <t>104144-1</t>
+  </si>
+  <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_A05-TypeDocComplementaire/FHIR/TRE-A05-TypeDocComplementaire</t>
   </si>
   <si>
@@ -477,6 +483,9 @@
   </si>
   <si>
     <t>PRESC-ORTHOPTIE</t>
+  </si>
+  <si>
+    <t>JUSTIF-PRESC-RENF</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_A12-NomenclatureASTM/FHIR/TRE-A12-NomenclatureASTM</t>
@@ -758,7 +767,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1795,6 +1804,32 @@
         <v>35</v>
       </c>
       <c r="E79" s="2"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B80" s="2"/>
+      <c r="C80" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D80" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="E80" s="2"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="B81" s="2"/>
+      <c r="C81" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D81" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="E81" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -1803,7 +1838,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1825,7 +1860,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -1842,7 +1877,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
@@ -1855,7 +1890,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
@@ -1868,7 +1903,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
@@ -1881,7 +1916,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
@@ -1894,7 +1929,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
@@ -1907,7 +1942,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
@@ -1920,7 +1955,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
@@ -1933,7 +1968,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
@@ -1946,7 +1981,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
@@ -1959,7 +1994,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
@@ -1972,7 +2007,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
@@ -1985,7 +2020,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
@@ -1998,7 +2033,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
@@ -2011,7 +2046,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
@@ -2024,7 +2059,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
@@ -2037,7 +2072,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -2050,7 +2085,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -2063,7 +2098,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
@@ -2076,7 +2111,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
@@ -2089,7 +2124,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
@@ -2102,7 +2137,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
@@ -2115,7 +2150,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -2128,20 +2163,20 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -2154,7 +2189,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -2167,7 +2202,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -2180,7 +2215,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -2193,7 +2228,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -2206,7 +2241,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -2219,7 +2254,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -2232,7 +2267,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -2242,6 +2277,19 @@
         <v>66</v>
       </c>
       <c r="E33" s="2"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="E34" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2272,7 +2320,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -2281,7 +2329,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -2289,14 +2337,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E3" s="2"/>
     </row>

--- a/ig/DM-OCTOBRE-2026/ASS-X16-CorrespondanceType-Classe-DMP.xlsx
+++ b/ig/DM-OCTOBRE-2026/ASS-X16-CorrespondanceType-Classe-DMP.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="158">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20261102120000</t>
+    <t>20240927120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-11-02T12:00:00+01:00</t>
+    <t>2024-09-27T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -380,12 +380,6 @@
     <t>101881-1</t>
   </si>
   <si>
-    <t>85895-1</t>
-  </si>
-  <si>
-    <t>104144-1</t>
-  </si>
-  <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_A05-TypeDocComplementaire/FHIR/TRE-A05-TypeDocComplementaire</t>
   </si>
   <si>
@@ -483,9 +477,6 @@
   </si>
   <si>
     <t>PRESC-ORTHOPTIE</t>
-  </si>
-  <si>
-    <t>JUSTIF-PRESC-RENF</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_A12-NomenclatureASTM/FHIR/TRE-A12-NomenclatureASTM</t>
@@ -767,7 +758,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1804,32 +1795,6 @@
         <v>35</v>
       </c>
       <c r="E79" s="2"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="B80" s="2"/>
-      <c r="C80" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D80" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="E80" s="2"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="B81" s="2"/>
-      <c r="C81" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D81" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="E81" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -1838,7 +1803,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1860,7 +1825,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -1877,7 +1842,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
@@ -1890,7 +1855,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
@@ -1903,7 +1868,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
@@ -1916,7 +1881,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
@@ -1929,7 +1894,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
@@ -1942,7 +1907,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
@@ -1955,7 +1920,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
@@ -1968,7 +1933,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
@@ -1981,7 +1946,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
@@ -1994,7 +1959,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
@@ -2007,7 +1972,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
@@ -2020,7 +1985,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
@@ -2033,7 +1998,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
@@ -2046,7 +2011,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
@@ -2059,7 +2024,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
@@ -2072,7 +2037,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -2085,7 +2050,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -2098,7 +2063,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
@@ -2111,7 +2076,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
@@ -2124,7 +2089,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
@@ -2137,7 +2102,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
@@ -2150,7 +2115,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -2163,20 +2128,20 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -2189,7 +2154,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -2202,7 +2167,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -2215,7 +2180,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -2228,7 +2193,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -2241,7 +2206,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -2254,7 +2219,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -2267,7 +2232,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -2277,19 +2242,6 @@
         <v>66</v>
       </c>
       <c r="E33" s="2"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="B34" s="2"/>
-      <c r="C34" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D34" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="E34" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2320,7 +2272,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -2329,7 +2281,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -2337,14 +2289,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E3" s="2"/>
     </row>
